--- a/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T16:54:59+00:00</t>
+    <t>2025-02-11T12:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2351,10 +2351,7 @@
   </si>
   <si>
     <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
+Valeurs possibles : ORG | APP | PER | CAB</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
@@ -23709,7 +23706,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>102</v>
@@ -24928,7 +24925,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>102</v>
@@ -25610,7 +25607,7 @@
         <v>85</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>84</v>
@@ -26559,7 +26556,7 @@
         <v>85</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>84</v>
@@ -26692,7 +26689,7 @@
         <v>85</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>84</v>
